--- a/Form-Layout_SDA/ImportLayouts/Config/RPT_Import_Map_2026.NEW.xlsx
+++ b/Form-Layout_SDA/ImportLayouts/Config/RPT_Import_Map_2026.NEW.xlsx
@@ -1560,47 +1560,47 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.Purchase Quotation_ใบเสนอราคาซื้อ.rpt</t>
+          <t xml:space="preserve">1.Purchase Request_TH_ใบขอซื้อ.rpt</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">3. Purchasing - AP\2. Purchase Quotation\1.Purchase Quotation_ใบเสนอราคาซื้อ</t>
+          <t xml:space="preserve">3. Purchasing - AP\1. Purchase Request\1.Purchase Request_TH_ใบขอซื้อ</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Purchase Quotation</t>
+          <t xml:space="preserve">Purchase Request</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">OPQT</t>
+          <t xml:space="preserve">OPRQ</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">PQT1</t>
+          <t xml:space="preserve">PRQ1</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">540000405</t>
+          <t xml:space="preserve">1470000113</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">540000405</t>
+          <t xml:space="preserve">1470000113</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Purchase Quotation - SDA</t>
+          <t xml:space="preserve">Purchase Request - SDA</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t xml:space="preserve">ใบเสนอราคาซื้อ</t>
+          <t xml:space="preserve">ใบขอซื้อ</t>
         </is>
       </c>
     </row>
@@ -1615,47 +1615,47 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.Purchase Order_ENG_ใบสั่งซื้อ.rpt</t>
+          <t xml:space="preserve">1.Purchase Quotation_ใบเสนอราคาซื้อ.rpt</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">3. Purchasing - AP\3. Purchase Order\1.Purchase Order_TH_ใบสั่งซื้อ</t>
+          <t xml:space="preserve">3. Purchasing - AP\2. Purchase Quotation\1.Purchase Quotation_ใบเสนอราคาซื้อ</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Purchase Order</t>
+          <t xml:space="preserve">Purchase Quotation</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">OPOR</t>
+          <t xml:space="preserve">OPQT</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">POR1</t>
+          <t xml:space="preserve">PQT1</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">540000405</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">142</t>
+          <t xml:space="preserve">540000405</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Purchase Order EN - SDA</t>
+          <t xml:space="preserve">Purchase Quotation - SDA</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t xml:space="preserve">ภาษาอังกฤษ</t>
+          <t xml:space="preserve">ใบเสนอราคาซื้อ</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.Purchase Order_TH_ใบสั่งซื้อ.rpt</t>
+          <t xml:space="preserve">1.Purchase Order_ENG_ใบสั่งซื้อ.rpt</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1705,12 +1705,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Purchase Order - SDA</t>
+          <t xml:space="preserve">Purchase Order EN - SDA</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t xml:space="preserve">ใบสั่งซื้อ</t>
+          <t xml:space="preserve">ภาษาอังกฤษ</t>
         </is>
       </c>
     </row>
@@ -1725,47 +1725,47 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.Goods Reciept PO_TH_ใบรับสินค้า_(Batch_Serial).rpt</t>
+          <t xml:space="preserve">1.Purchase Order_TH_ใบสั่งซื้อ.rpt</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">3. Purchasing - AP\4. Goods Receipt PO\2.Goods Receive PO_TH_ใบรับสินค้า_(Batch_Serial) - Copy</t>
+          <t xml:space="preserve">3. Purchasing - AP\3. Purchase Order\1.Purchase Order_TH_ใบสั่งซื้อ</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goods Receipt PO</t>
+          <t xml:space="preserve">Purchase Order</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">OPDN</t>
+          <t xml:space="preserve">OPOR</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDN1</t>
+          <t xml:space="preserve">POR1</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">143</t>
+          <t xml:space="preserve">142</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">GRPO (B/S) - SDA</t>
+          <t xml:space="preserve">Purchase Order - SDA</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">รับสินค้าจากการซื้อ</t>
+          <t xml:space="preserve">ใบสั่งซื้อ</t>
         </is>
       </c>
     </row>
@@ -1780,47 +1780,47 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.Goods Return_TH_ใบส่งคืนสินค้า_(Batch_Serial).rpt</t>
+          <t xml:space="preserve">1.Goods Reciept PO_TH_ใบรับสินค้า_(Batch_Serial).rpt</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">3. Purchasing - AP\5. Goods Return\2.Goods Return_EN_ใบส่งคืนสินค้า_(Batch_Serial)</t>
+          <t xml:space="preserve">3. Purchasing - AP\4. Goods Receipt PO\2.Goods Receive PO_TH_ใบรับสินค้า_(Batch_Serial) - Copy</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goods Return</t>
+          <t xml:space="preserve">Goods Receipt PO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORPD</t>
+          <t xml:space="preserve">OPDN</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">RPD1</t>
+          <t xml:space="preserve">PDN1</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">144</t>
+          <t xml:space="preserve">143</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goods Return (B/S) - SDA</t>
+          <t xml:space="preserve">GRPO (B/S) - SDA</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">ใบส่งคืนสินค้า</t>
+          <t xml:space="preserve">รับสินค้าจากการซื้อ</t>
         </is>
       </c>
     </row>
@@ -1835,47 +1835,47 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.AP Down Payment_ENG ใบจ่ายเงินมัดจำ.rpt</t>
+          <t xml:space="preserve">1.Goods Return_TH_ใบส่งคืนสินค้า_(Batch_Serial).rpt</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">3. Purchasing - AP\6. AP Down Payment Invoice\1.AP Down Payment ใบจ่ายเงินมัดจำ</t>
+          <t xml:space="preserve">3. Purchasing - AP\5. Goods Return\2.Goods Return_EN_ใบส่งคืนสินค้า_(Batch_Serial)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">AP Down Payment</t>
+          <t xml:space="preserve">Goods Return</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">ODPO</t>
+          <t xml:space="preserve">ORPD</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">DPO1</t>
+          <t xml:space="preserve">RPD1</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">204</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">65301</t>
+          <t xml:space="preserve">144</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">AP DP EN - SDA</t>
+          <t xml:space="preserve">Goods Return (B/S) - SDA</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">ภาษาอังกฤษ</t>
+          <t xml:space="preserve">ใบส่งคืนสินค้า</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.AP Down Payment_ใบจ่ายเงินมัดจำ.rpt</t>
+          <t xml:space="preserve">1.AP Down Payment_ENG ใบจ่ายเงินมัดจำ.rpt</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">AP DP - SDA</t>
+          <t xml:space="preserve">AP DP EN - SDA</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t xml:space="preserve">AP Down Payment_ใบจ่ายเงินมัดจำ</t>
+          <t xml:space="preserve">ภาษาอังกฤษ</t>
         </is>
       </c>
     </row>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.AP Down Payment Invoice_ENG ใบจ่ายเงินมัดจำใบกำกับภาษี.rpt</t>
+          <t xml:space="preserve">1.AP Down Payment_ใบจ่ายเงินมัดจำ.rpt</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">3. Purchasing - AP\6. AP Down Payment Invoice\2.AP Down Payment Invoice_ใบจ่ายเงินมัดจำ_ใบแจ้งหนี้</t>
+          <t xml:space="preserve">3. Purchasing - AP\6. AP Down Payment Invoice\1.AP Down Payment ใบจ่ายเงินมัดจำ</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve">AP DP Tax EN - SDA</t>
+          <t xml:space="preserve">AP DP - SDA</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t xml:space="preserve">ภาษาอังกฤษ</t>
+          <t xml:space="preserve">AP Down Payment_ใบจ่ายเงินมัดจำ</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.AP Down Payment Invoice_ใบจ่ายเงินมัดจำใบกำกับภาษี.rpt</t>
+          <t xml:space="preserve">2.AP Down Payment Invoice_ENG ใบจ่ายเงินมัดจำใบกำกับภาษี.rpt</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2035,12 +2035,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">AP DP Tax - SDA</t>
+          <t xml:space="preserve">AP DP Tax EN - SDA</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t xml:space="preserve">ใบจ่ายเงินมัดจำ+กำกับ</t>
+          <t xml:space="preserve">ภาษาอังกฤษ</t>
         </is>
       </c>
     </row>
@@ -2055,47 +2055,47 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.AP Invoice_ใบแจ้งหนี้_(Batch_Serial).rpt</t>
+          <t xml:space="preserve">2.AP Down Payment Invoice_ใบจ่ายเงินมัดจำใบกำกับภาษี.rpt</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">3. Purchasing - AP\7. AP Invoice\2.AP Invoice_ใบแจ้งหนี้_(Batch_Serial)</t>
+          <t xml:space="preserve">3. Purchasing - AP\6. AP Down Payment Invoice\2.AP Down Payment Invoice_ใบจ่ายเงินมัดจำ_ใบแจ้งหนี้</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">AP Invoice</t>
+          <t xml:space="preserve">AP Down Payment</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">OPCH</t>
+          <t xml:space="preserve">ODPO</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">PCH1</t>
+          <t xml:space="preserve">DPO1</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">204</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">141</t>
+          <t xml:space="preserve">65301</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve">AP Invoice (B/S) - SDA</t>
+          <t xml:space="preserve">AP DP Tax - SDA</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Batch/Serial</t>
+          <t xml:space="preserve">ใบจ่ายเงินมัดจำ+กำกับ</t>
         </is>
       </c>
     </row>
@@ -2110,47 +2110,47 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.AP Credit Memo_ใบลดหนี้.rpt</t>
+          <t xml:space="preserve">1.AP Invoice_ใบแจ้งหนี้_(Batch_Serial).rpt</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">3. Purchasing - AP\8. AP Credit Memo\1.AP Credit Memo_ใบลดหนี้</t>
+          <t xml:space="preserve">3. Purchasing - AP\7. AP Invoice\2.AP Invoice_ใบแจ้งหนี้_(Batch_Serial)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">AP Credit Memo</t>
+          <t xml:space="preserve">AP Invoice</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORPC</t>
+          <t xml:space="preserve">OPCH</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">RPC1</t>
+          <t xml:space="preserve">PCH1</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">181</t>
+          <t xml:space="preserve">141</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t xml:space="preserve">AP Credit Memo - SDA</t>
+          <t xml:space="preserve">AP Invoice (B/S) - SDA</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">ใบลดหนี้ซื้อ</t>
+          <t xml:space="preserve">Batch/Serial</t>
         </is>
       </c>
     </row>
@@ -2165,47 +2165,47 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.Landed Costs_ใบปรับราคาต้นทุนสินค้า.rpt</t>
+          <t xml:space="preserve">1.AP Credit Memo_ใบลดหนี้.rpt</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">3. Purchasing - AP\9. Landed Costs\1.Landed Costs_ใบปรับราคาต้นทุนสินค้า</t>
+          <t xml:space="preserve">3. Purchasing - AP\8. AP Credit Memo\1.AP Credit Memo_ใบลดหนี้</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landed Costs</t>
+          <t xml:space="preserve">AP Credit Memo</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">OIPF</t>
+          <t xml:space="preserve">ORPC</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">IPF1</t>
+          <t xml:space="preserve">RPC1</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">69</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">992</t>
+          <t xml:space="preserve">181</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landed Costs - SDA</t>
+          <t xml:space="preserve">AP Credit Memo - SDA</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">ปรับต้นทุน</t>
+          <t xml:space="preserve">ใบลดหนี้ซื้อ</t>
         </is>
       </c>
     </row>
@@ -2215,52 +2215,52 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales - AR</t>
+          <t xml:space="preserve">Purchasing - AP</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.Sale Quotation_ใบเสนอราคาขาย_(BOM) ENG.rpt</t>
+          <t xml:space="preserve">1.Landed Costs_ใบปรับราคาต้นทุนสินค้า.rpt</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. Sales - AR\1. Sales Quotation\1.Sale Quotation_ใบเสนอราคาขาย(BOM)</t>
+          <t xml:space="preserve">3. Purchasing - AP\9. Landed Costs\1.Landed Costs_ใบปรับราคาต้นทุนสินค้า</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Quotation</t>
+          <t xml:space="preserve">Landed Costs</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">OQUT</t>
+          <t xml:space="preserve">OIPF</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUT1</t>
+          <t xml:space="preserve">IPF1</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">69</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">149</t>
+          <t xml:space="preserve">992</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Quotation (BOM) EN - SDA</t>
+          <t xml:space="preserve">Landed Costs - SDA</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">ภาษาอังกฤษ BOM</t>
+          <t xml:space="preserve">ปรับต้นทุน</t>
         </is>
       </c>
     </row>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.Sale Quotation_ใบเสนอราคาขาย_(Bom).rpt</t>
+          <t xml:space="preserve">1.Sale Quotation_ใบเสนอราคาขาย_(BOM) ENG.rpt</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2310,12 +2310,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Quotation (BOM) - SDA</t>
+          <t xml:space="preserve">Sales Quotation (BOM) EN - SDA</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">รองรับ BOM</t>
+          <t xml:space="preserve">ภาษาอังกฤษ BOM</t>
         </is>
       </c>
     </row>
@@ -2330,12 +2330,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.Sale Quotation_ใบเสนอราคาขาย_(Dis) ENG.rpt</t>
+          <t xml:space="preserve">1.Sale Quotation_ใบเสนอราคาขาย_(Bom).rpt</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. Sales - AR\1. Sales Quotation\2.Sale Quotation_ใบเสนอราคาขาย_(Dis)</t>
+          <t xml:space="preserve">2. Sales - AR\1. Sales Quotation\1.Sale Quotation_ใบเสนอราคาขาย(BOM)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2365,12 +2365,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Quotation (Dis) EN - SDA</t>
+          <t xml:space="preserve">Sales Quotation (BOM) - SDA</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">ภาษาอังกฤษ Dis</t>
+          <t xml:space="preserve">รองรับ BOM</t>
         </is>
       </c>
     </row>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.Sale Quotation_ใบเสนอราคาขาย_(Dis).rpt</t>
+          <t xml:space="preserve">2.Sale Quotation_ใบเสนอราคาขาย_(Dis) ENG.rpt</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Quotation (Dis) - SDA</t>
+          <t xml:space="preserve">Sales Quotation (Dis) EN - SDA</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">รองรับส่วนลด</t>
+          <t xml:space="preserve">ภาษาอังกฤษ Dis</t>
         </is>
       </c>
     </row>
@@ -2440,42 +2440,42 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.Sale Order_ใบสั่งขาย_(Dis).rpt</t>
+          <t xml:space="preserve">2.Sale Quotation_ใบเสนอราคาขาย_(Dis).rpt</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. Sales - AR\2. Sales Order\1.Sale Order_ใบสั่งขาย_(Dis)</t>
+          <t xml:space="preserve">2. Sales - AR\1. Sales Quotation\2.Sale Quotation_ใบเสนอราคาขาย_(Dis)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Order</t>
+          <t xml:space="preserve">Sales Quotation</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORDR</t>
+          <t xml:space="preserve">OQUT</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">RDR1</t>
+          <t xml:space="preserve">QUT1</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">139</t>
+          <t xml:space="preserve">149</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Order (Dis) - SDA</t>
+          <t xml:space="preserve">Sales Quotation (Dis) - SDA</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.Sale Order_ใบสั่งขาย_(Bom).rpt</t>
+          <t xml:space="preserve">1.Sale Order_ใบสั่งขาย_(Dis).rpt</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. Sales - AR\2. Sales Order\3.Sale Order_ใบสั่งขาย_(Bomm)</t>
+          <t xml:space="preserve">2. Sales - AR\2. Sales Order\1.Sale Order_ใบสั่งขาย_(Dis)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Order (BOM) - SDA</t>
+          <t xml:space="preserve">Sales Order (Dis) - SDA</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">รองรับ BOM</t>
+          <t xml:space="preserve">รองรับส่วนลด</t>
         </is>
       </c>
     </row>
@@ -2550,47 +2550,47 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.Delivery_ใบส่งของ_(Batch_Serial).rpt</t>
+          <t xml:space="preserve">2.Sale Order_ใบสั่งขาย_(Bom).rpt</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. Sales - AR\3. Delivery\2.Delivery_ใบส่งของ_(Batch_Serial)</t>
+          <t xml:space="preserve">2. Sales - AR\2. Sales Order\3.Sale Order_ใบสั่งขาย_(Bomm)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delivery</t>
+          <t xml:space="preserve">Sales Order</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">ODLN</t>
+          <t xml:space="preserve">ORDR</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">DLN1</t>
+          <t xml:space="preserve">RDR1</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">140</t>
+          <t xml:space="preserve">139</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delivery (B/S) - SDA</t>
+          <t xml:space="preserve">Sales Order (BOM) - SDA</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Batch/Serial</t>
+          <t xml:space="preserve">รองรับ BOM</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.Delivery_ใบส่งของ_Eng (Batch_Serial).rpt</t>
+          <t xml:space="preserve">1.Delivery_ใบส่งของ_(Batch_Serial).rpt</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2640,12 +2640,12 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delivery (B/S) EN - SDA</t>
+          <t xml:space="preserve">Delivery (B/S) - SDA</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">ภาษาอังกฤษ</t>
+          <t xml:space="preserve">Batch/Serial</t>
         </is>
       </c>
     </row>
@@ -2660,47 +2660,47 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.Retrun_ใบรับคืนสินค้า_(Batch_Serial).rpt</t>
+          <t xml:space="preserve">1.Delivery_ใบส่งของ_Eng (Batch_Serial).rpt</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. Sales - AR\4. Return\2.Retrun_ใบรับคืนสินค้า_(Batch_Serial)</t>
+          <t xml:space="preserve">2. Sales - AR\3. Delivery\2.Delivery_ใบส่งของ_(Batch_Serial)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Return</t>
+          <t xml:space="preserve">Delivery</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORDN</t>
+          <t xml:space="preserve">ODLN</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">RDN1</t>
+          <t xml:space="preserve">DLN1</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">141</t>
+          <t xml:space="preserve">140</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Return (B/S) - SDA</t>
+          <t xml:space="preserve">Delivery (B/S) EN - SDA</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Batch/Serial</t>
+          <t xml:space="preserve">ภาษาอังกฤษ</t>
         </is>
       </c>
     </row>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.Retrun_ใบรับคืนสินค้า_ENG (Batch_Serial).rpt</t>
+          <t xml:space="preserve">1.Retrun_ใบรับคืนสินค้า_(Batch_Serial).rpt</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Return (B/S) EN - SDA</t>
+          <t xml:space="preserve">Return (B/S) - SDA</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Batch/Serial + ภาษาอังกฤษ</t>
+          <t xml:space="preserve">Batch/Serial</t>
         </is>
       </c>
     </row>
@@ -2770,47 +2770,47 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.AR Down Payment_BOM ใบเสร็จรับเงินมัดจำ.rpt</t>
+          <t xml:space="preserve">1.Retrun_ใบรับคืนสินค้า_ENG (Batch_Serial).rpt</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. Sales - AR\5. AR Down Payment Invoice\1.AR Down Payment_ใบเสร็จรับเงินมัดจำ</t>
+          <t xml:space="preserve">2. Sales - AR\4. Return\2.Retrun_ใบรับคืนสินค้า_(Batch_Serial)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">AR Down Payment</t>
+          <t xml:space="preserve">Return</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">ODPI</t>
+          <t xml:space="preserve">ORDN</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">DPI1</t>
+          <t xml:space="preserve">RDN1</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">203</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">65300</t>
+          <t xml:space="preserve">141</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">AR DP (BOM) - SDA</t>
+          <t xml:space="preserve">Return (B/S) EN - SDA</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">รองรับ BOM</t>
+          <t xml:space="preserve">Batch/Serial + ภาษาอังกฤษ</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.AR Down Payment_BOM_ENG ใบเสร็จรับเงินมัดจำ.rpt</t>
+          <t xml:space="preserve">1.AR Down Payment_BOM ใบเสร็จรับเงินมัดจำ.rpt</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">AR DP (BOM) EN - SDA</t>
+          <t xml:space="preserve">AR DP (BOM) - SDA</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">รองรับ BOM + ภาษาอังกฤษ</t>
+          <t xml:space="preserve">รองรับ BOM</t>
         </is>
       </c>
     </row>
@@ -2880,12 +2880,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.AR Down PaymentTax Invoice_BOM ใบเสร็จรับเงินมัดจำใบกำกับภาษี.rpt</t>
+          <t xml:space="preserve">1.AR Down Payment_BOM_ENG ใบเสร็จรับเงินมัดจำ.rpt</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. Sales - AR\5. AR Down Payment Invoice\2.AR Down PaymentTax Invoice_ใบเสร็จรับเงินมัดจำใบกำกับภาษี</t>
+          <t xml:space="preserve">2. Sales - AR\5. AR Down Payment Invoice\1.AR Down Payment_ใบเสร็จรับเงินมัดจำ</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">AR DP Tax (BOM) - SDA</t>
+          <t xml:space="preserve">AR DP (BOM) EN - SDA</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t xml:space="preserve">รองรับ BOM</t>
+          <t xml:space="preserve">รองรับ BOM + ภาษาอังกฤษ</t>
         </is>
       </c>
     </row>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.AR Down PaymentTax Invoice_BOM_ENG ใบเสร็จรับเงินมัดจำใบกำกับภาษี.rpt</t>
+          <t xml:space="preserve">2.AR Down PaymentTax Invoice_BOM ใบเสร็จรับเงินมัดจำใบกำกับภาษี.rpt</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">AR DP Tax (BOM) EN - SDA</t>
+          <t xml:space="preserve">AR DP Tax (BOM) - SDA</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">รองรับ BOM + ภาษาอังกฤษ</t>
+          <t xml:space="preserve">รองรับ BOM</t>
         </is>
       </c>
     </row>
@@ -2990,12 +2990,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.AR Down Payment Invoice_BOM ใบแจ้งหนี้เงินค่ามัดจำใบกำกับภาษี.rpt</t>
+          <t xml:space="preserve">2.AR Down PaymentTax Invoice_BOM_ENG ใบเสร็จรับเงินมัดจำใบกำกับภาษี.rpt</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. Sales - AR\5. AR Down Payment Invoice\3.AR Down Payment Invoice_ใบแจ้งหนี้เงินค่ามัดจำใบกำกับภาษี</t>
+          <t xml:space="preserve">2. Sales - AR\5. AR Down Payment Invoice\2.AR Down PaymentTax Invoice_ใบเสร็จรับเงินมัดจำใบกำกับภาษี</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">AR DP Invoice Tax (BOM) - SDA</t>
+          <t xml:space="preserve">AR DP Tax (BOM) EN - SDA</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">รองรับ BOM</t>
+          <t xml:space="preserve">รองรับ BOM + ภาษาอังกฤษ</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.AR Down PaymentTax Invoice_BOM_ENG ใบแจ้งหนี้เงินค่ามัดจำใบกำกับภาษี.rpt</t>
+          <t xml:space="preserve">3.AR Down Payment Invoice_BOM ใบแจ้งหนี้เงินค่ามัดจำใบกำกับภาษี.rpt</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">AR DP Invoice Tax (BOM) EN - SDA</t>
+          <t xml:space="preserve">AR DP Invoice Tax (BOM) - SDA</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">รองรับ BOM + ภาษาอังกฤษ</t>
+          <t xml:space="preserve">รองรับ BOM</t>
         </is>
       </c>
     </row>
@@ -3100,47 +3100,47 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.AR Invoice_ENG ใบแจ้งหนี้_(Dis).rpt</t>
+          <t xml:space="preserve">3.AR Down PaymentTax Invoice_BOM_ENG ใบแจ้งหนี้เงินค่ามัดจำใบกำกับภาษี.rpt</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. Sales - AR\6. AR Invoice\2.AR Invoice_ใบแจ้งหนี้_(Dis)</t>
+          <t xml:space="preserve">2. Sales - AR\5. AR Down Payment Invoice\3.AR Down Payment Invoice_ใบแจ้งหนี้เงินค่ามัดจำใบกำกับภาษี</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">AR Invoice</t>
+          <t xml:space="preserve">AR Down Payment</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">OINV</t>
+          <t xml:space="preserve">ODPI</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">INV1</t>
+          <t xml:space="preserve">DPI1</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">203</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">133</t>
+          <t xml:space="preserve">65300</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">AR Invoice (Dis) EN - SDA</t>
+          <t xml:space="preserve">AR DP Invoice Tax (BOM) EN - SDA</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">รองรับส่วนลด + ภาษาอังกฤษ</t>
+          <t xml:space="preserve">รองรับ BOM + ภาษาอังกฤษ</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.AR Invoice_ใบแจ้งหนี้_(Dis).rpt</t>
+          <t xml:space="preserve">1.AR Invoice_ENG ใบแจ้งหนี้_(Dis).rpt</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3190,12 +3190,12 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">AR Invoice (Dis) - SDA</t>
+          <t xml:space="preserve">AR Invoice (Dis) EN - SDA</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">รองรับส่วนลด</t>
+          <t xml:space="preserve">รองรับส่วนลด + ภาษาอังกฤษ</t>
         </is>
       </c>
     </row>
@@ -3210,12 +3210,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.BillingAR InvoiceTax Invoice_ENG ใบวางบิลใบแจ้งหนี้ใบกำกับภาษี (Dis).rpt</t>
+          <t xml:space="preserve">1.AR Invoice_ใบแจ้งหนี้_(Dis).rpt</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. Sales - AR\6. AR Invoice\4.BillingAR InvoiceTax Invoice_ใบวางบิลใบแจ้งหนี้ใบกำกับภาษี (Dis)</t>
+          <t xml:space="preserve">2. Sales - AR\6. AR Invoice\2.AR Invoice_ใบแจ้งหนี้_(Dis)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">AR Invoice Billing Tax (Dis) EN - SDA</t>
+          <t xml:space="preserve">AR Invoice (Dis) - SDA</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">รองรับส่วนลด + ภาษาอังกฤษ</t>
+          <t xml:space="preserve">รองรับส่วนลด</t>
         </is>
       </c>
     </row>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.BillingAR InvoiceTax Invoice_ใบวางบิลใบแจ้งหนี้ใบกำกับภาษี (Dis).rpt</t>
+          <t xml:space="preserve">2.BillingAR InvoiceTax Invoice_ENG ใบวางบิลใบแจ้งหนี้ใบกำกับภาษี (Dis).rpt</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">AR Invoice Billing Tax (Dis) - SDA</t>
+          <t xml:space="preserve">AR Invoice Billing Tax (Dis) EN - SDA</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">รองรับส่วนลด</t>
+          <t xml:space="preserve">รองรับส่วนลด + ภาษาอังกฤษ</t>
         </is>
       </c>
     </row>
@@ -3320,12 +3320,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.BillingAR Invoice_ENG ใบวางบิลใบแจ้งหนี้ (Dis).rpt</t>
+          <t xml:space="preserve">2.BillingAR InvoiceTax Invoice_ใบวางบิลใบแจ้งหนี้ใบกำกับภาษี (Dis).rpt</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. Sales - AR\6. AR Invoice\6.BillingAR Invoice_ใบวางบิลใบแจ้งหนี้ (Dis)</t>
+          <t xml:space="preserve">2. Sales - AR\6. AR Invoice\4.BillingAR InvoiceTax Invoice_ใบวางบิลใบแจ้งหนี้ใบกำกับภาษี (Dis)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">AR Invoice Billing (Dis) EN - SDA</t>
+          <t xml:space="preserve">AR Invoice Billing Tax (Dis) - SDA</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">รองรับส่วนลด + ภาษาอังกฤษ</t>
+          <t xml:space="preserve">รองรับส่วนลด</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.BillingAR Invoice_ใบวางบิลใบแจ้งหนี้ (Dis).rpt</t>
+          <t xml:space="preserve">3.BillingAR Invoice_ENG ใบวางบิลใบแจ้งหนี้ (Dis).rpt</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3410,12 +3410,12 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">AR Invoice Billing (Dis) - SDA</t>
+          <t xml:space="preserve">AR Invoice Billing (Dis) EN - SDA</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">รองรับส่วนลด</t>
+          <t xml:space="preserve">รองรับส่วนลด + ภาษาอังกฤษ</t>
         </is>
       </c>
     </row>
@@ -3430,47 +3430,47 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.AR_Credit Memo_ใบลดหนี้_(Batch_Serial) (Dis).rpt</t>
+          <t xml:space="preserve">3.BillingAR Invoice_ใบวางบิลใบแจ้งหนี้ (Dis).rpt</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. Sales - AR\7. AR Credit Memo\4.AR_Credit Memo_ใบลดหนี้_(Batch_Serial) (Dis)</t>
+          <t xml:space="preserve">2. Sales - AR\6. AR Invoice\6.BillingAR Invoice_ใบวางบิลใบแจ้งหนี้ (Dis)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">AR Credit Memo</t>
+          <t xml:space="preserve">AR Invoice</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORIN</t>
+          <t xml:space="preserve">OINV</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">RIN1</t>
+          <t xml:space="preserve">INV1</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">179</t>
+          <t xml:space="preserve">133</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">AR CM (B/S+Dis) - SDA</t>
+          <t xml:space="preserve">AR Invoice Billing (Dis) - SDA</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/S + ส่วนลด</t>
+          <t xml:space="preserve">รองรับส่วนลด</t>
         </is>
       </c>
     </row>
@@ -3485,51 +3485,106 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
+          <t xml:space="preserve">1.AR_Credit Memo_ใบลดหนี้_(Batch_Serial) (Dis).rpt</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. Sales - AR\7. AR Credit Memo\4.AR_Credit Memo_ใบลดหนี้_(Batch_Serial) (Dis)</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR Credit Memo</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ORIN</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RIN1</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR CM (B/S+Dis) - SDA</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B/S + ส่วนลด</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sales - AR</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
           <t xml:space="preserve">1.AR_Credit Memo_ใบลดหนี้_ENG (Batch_Serial) (Dis).rpt</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t xml:space="preserve">2. Sales - AR\7. AR Credit Memo\4.AR_Credit Memo_ใบลดหนี้_(Batch_Serial) (Dis)</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t xml:space="preserve">AR Credit Memo</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t xml:space="preserve">ORIN</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t xml:space="preserve">RIN1</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t xml:space="preserve">14</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t xml:space="preserve">179</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t xml:space="preserve">AR CM (B/S+Dis) EN - SDA</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t xml:space="preserve">Batch/Serial + รองรับส่วนลด + ภาษาอังกฤษ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K63"/>
+  <autoFilter ref="A1:K64"/>
 </worksheet>
 </file>
--- a/Form-Layout_SDA/ImportLayouts/Config/RPT_Import_Map_2026.NEW.xlsx
+++ b/Form-Layout_SDA/ImportLayouts/Config/RPT_Import_Map_2026.NEW.xlsx
@@ -2830,7 +2830,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. Sales - AR\5. AR Down Payment Invoice\1.AR Down Payment_ใบเสร็จรับเงินมัดจำ</t>
+          <t xml:space="preserve">2. Sales - AR\5. AR Down Payment Invoice\1. AR Down Payment Invoice_BOM\1.AR Down Payment_ใบเสร็จรับเงินมัดจำ</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. Sales - AR\5. AR Down Payment Invoice\1.AR Down Payment_ใบเสร็จรับเงินมัดจำ</t>
+          <t xml:space="preserve">2. Sales - AR\5. AR Down Payment Invoice\1. AR Down Payment Invoice_BOM\1.AR Down Payment_ใบเสร็จรับเงินมัดจำ</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. Sales - AR\5. AR Down Payment Invoice\2.AR Down PaymentTax Invoice_ใบเสร็จรับเงินมัดจำใบกำกับภาษี</t>
+          <t xml:space="preserve">2. Sales - AR\5. AR Down Payment Invoice\1. AR Down Payment Invoice_BOM\2.AR Down PaymentTax Invoice_ใบเสร็จรับเงินมัดจำใบกำกับภาษี</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. Sales - AR\5. AR Down Payment Invoice\2.AR Down PaymentTax Invoice_ใบเสร็จรับเงินมัดจำใบกำกับภาษี</t>
+          <t xml:space="preserve">2. Sales - AR\5. AR Down Payment Invoice\1. AR Down Payment Invoice_BOM\2.AR Down PaymentTax Invoice_ใบเสร็จรับเงินมัดจำใบกำกับภาษี</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. Sales - AR\5. AR Down Payment Invoice\3.AR Down Payment Invoice_ใบแจ้งหนี้เงินค่ามัดจำใบกำกับภาษี</t>
+          <t xml:space="preserve">2. Sales - AR\5. AR Down Payment Invoice\1. AR Down Payment Invoice_BOM\3.AR Down Payment Invoice_ใบแจ้งหนี้เงินค่ามัดจำใบกำกับภาษี</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. Sales - AR\5. AR Down Payment Invoice\3.AR Down Payment Invoice_ใบแจ้งหนี้เงินค่ามัดจำใบกำกับภาษี</t>
+          <t xml:space="preserve">2. Sales - AR\5. AR Down Payment Invoice\1. AR Down Payment Invoice_BOM\3.AR Down Payment Invoice_ใบแจ้งหนี้เงินค่ามัดจำใบกำกับภาษี</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. Sales - AR\6. AR Invoice\2.AR Invoice_ใบแจ้งหนี้_(Dis)</t>
+          <t xml:space="preserve">2. Sales - AR\6. AR Invoice\1.AR Invoice_Dis\1.AR Invoice_ใบแจ้งหนี้</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. Sales - AR\6. AR Invoice\2.AR Invoice_ใบแจ้งหนี้_(Dis)</t>
+          <t xml:space="preserve">2. Sales - AR\6. AR Invoice\1.AR Invoice_Dis\1.AR Invoice_ใบแจ้งหนี้</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. Sales - AR\6. AR Invoice\4.BillingAR InvoiceTax Invoice_ใบวางบิลใบแจ้งหนี้ใบกำกับภาษี (Dis)</t>
+          <t xml:space="preserve">2. Sales - AR\6. AR Invoice\1.AR Invoice_Dis\2.BillingAR InvoiceTax Invoice_ใบวางบิลใบแจ้งหนี้ใบกำกับภาษี</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. Sales - AR\6. AR Invoice\4.BillingAR InvoiceTax Invoice_ใบวางบิลใบแจ้งหนี้ใบกำกับภาษี (Dis)</t>
+          <t xml:space="preserve">2. Sales - AR\6. AR Invoice\1.AR Invoice_Dis\2.BillingAR InvoiceTax Invoice_ใบวางบิลใบแจ้งหนี้ใบกำกับภาษี</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. Sales - AR\6. AR Invoice\6.BillingAR Invoice_ใบวางบิลใบแจ้งหนี้ (Dis)</t>
+          <t xml:space="preserve">2. Sales - AR\6. AR Invoice\1.AR Invoice_Dis\3.BillingAR Invoice_ใบวางบิลใบแจ้งหนี้</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. Sales - AR\6. AR Invoice\6.BillingAR Invoice_ใบวางบิลใบแจ้งหนี้ (Dis)</t>
+          <t xml:space="preserve">2. Sales - AR\6. AR Invoice\1.AR Invoice_Dis\3.BillingAR Invoice_ใบวางบิลใบแจ้งหนี้</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3485,47 +3485,47 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.AR_Credit Memo_ใบลดหนี้_(Batch_Serial) (Dis).rpt</t>
+          <t xml:space="preserve">1.AR Invoice_ENG ใบแจ้งหนี้_(Bom).rpt</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. Sales - AR\7. AR Credit Memo\4.AR_Credit Memo_ใบลดหนี้_(Batch_Serial) (Dis)</t>
+          <t xml:space="preserve">2. Sales - AR\6. AR Invoice\2.AR Invoice_BOM\1.AR Invoice_ใบแจ้งหนี้</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">AR Credit Memo</t>
+          <t xml:space="preserve">AR Invoice</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORIN</t>
+          <t xml:space="preserve">OINV</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">RIN1</t>
+          <t xml:space="preserve">INV1</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">179</t>
+          <t xml:space="preserve">133</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">AR CM (B/S+Dis) - SDA</t>
+          <t xml:space="preserve">AR Invoice (BOM) EN - SDA</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/S + ส่วนลด</t>
+          <t xml:space="preserve">รองรับ BOM + ภาษาอังกฤษ</t>
         </is>
       </c>
     </row>
@@ -3540,51 +3540,381 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
+          <t xml:space="preserve">1.AR Invoice_ใบแจ้งหนี้_(Bom).rpt</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. Sales - AR\6. AR Invoice\2.AR Invoice_BOM\1.AR Invoice_ใบแจ้งหนี้</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR Invoice</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OINV</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INV1</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR Invoice (BOM) - SDA</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">รองรับ BOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sales - AR</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.BillingAR InvoiceTax Invoice_ENG ใบวางบิลใบแจ้งหนี้ใบกำกับภาษี (Bom).rpt</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. Sales - AR\6. AR Invoice\2.AR Invoice_BOM\2.BillingAR InvoiceTax Invoice_ใบวางบิลใบแจ้งหนี้ใบกำกับภาษี</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR Invoice</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OINV</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INV1</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR Invoice Billing Tax (BOM) EN - SDA</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">รองรับ BOM + ภาษาอังกฤษ</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sales - AR</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.BillingAR InvoiceTax Invoice_ใบวางบิลใบแจ้งหนี้ใบกำกับภาษี (Bom).rpt</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. Sales - AR\6. AR Invoice\2.AR Invoice_BOM\2.BillingAR InvoiceTax Invoice_ใบวางบิลใบแจ้งหนี้ใบกำกับภาษี</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR Invoice</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OINV</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INV1</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR Invoice Billing Tax (BOM) - SDA</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">รองรับ BOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sales - AR</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.BillingAR Invoice_ENG ใบวางบิลใบแจ้งหนี้ (Bom).rpt</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. Sales - AR\6. AR Invoice\2.AR Invoice_BOM\3.BillingAR Invoice_ใบวางบิลใบแจ้งหนี้</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR Invoice</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OINV</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INV1</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR Invoice Billing (BOM) EN - SDA</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">รองรับ BOM + ภาษาอังกฤษ</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sales - AR</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.BillingAR Invoice_ใบวางบิลใบแจ้งหนี้ (Bom).rpt</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. Sales - AR\6. AR Invoice\2.AR Invoice_BOM\3.BillingAR Invoice_ใบวางบิลใบแจ้งหนี้</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR Invoice</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OINV</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INV1</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR Invoice Billing (BOM) - SDA</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">รองรับ BOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sales - AR</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.AR_Credit Memo_ใบลดหนี้_(Batch_Serial) (Dis).rpt</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. Sales - AR\7. AR Credit Memo\4.AR_Credit Memo_ใบลดหนี้_(Batch_Serial) (Dis)</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR Credit Memo</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ORIN</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RIN1</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR CM (B/S+Dis) - SDA</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B/S + ส่วนลด</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sales - AR</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
           <t xml:space="preserve">1.AR_Credit Memo_ใบลดหนี้_ENG (Batch_Serial) (Dis).rpt</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t xml:space="preserve">2. Sales - AR\7. AR Credit Memo\4.AR_Credit Memo_ใบลดหนี้_(Batch_Serial) (Dis)</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t xml:space="preserve">AR Credit Memo</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t xml:space="preserve">ORIN</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t xml:space="preserve">RIN1</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t xml:space="preserve">14</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t xml:space="preserve">179</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t xml:space="preserve">AR CM (B/S+Dis) EN - SDA</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t xml:space="preserve">Batch/Serial + รองรับส่วนลด + ภาษาอังกฤษ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K64"/>
+  <autoFilter ref="A1:K70"/>
 </worksheet>
 </file>